--- a/www/download/COUNTRY.HRV.WIOD16.xlsx
+++ b/www/download/COUNTRY.HRV.WIOD16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>Croácia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>8.26250375098198</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>8.33742146015543</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>7.84497710826126</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6.69501075730157</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>6.03039611910988</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>5.94244035252586</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>5.83273391080575</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>5.35551463931815</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>4.91173222839952</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>5.26570960989759</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>5.48696297090356</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>5.33388294586426</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>5.8481042850087</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>5.70102181343767</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>5.73563568952309</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>1.598</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1.578</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>1.603</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>1.633</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>1.637</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>1.683</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>1.719</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>1.78</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>1.768</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>1.696</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>1.632</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>1.572</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>1.531</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>1.57</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>1.247</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1.221</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>1.238</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>1.274</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>1.279</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>1.298</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>1.321</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>1.356</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>1.401</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>1.391</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>1.318</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>1.269</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1.254</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>1.246</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>1.304</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>3036.893</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3001.987</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>3056.057</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>3092.179</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>3137.303</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>3149.281</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>3240.171</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>3310.082</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>3438.268</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>3410.056</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>3294.414</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>3167.11</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>3022.4</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>2923.053</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2966.935</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2414.731</t>
+          <t>2986665720.73569</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2366.07</t>
+          <t>2927609795.61264</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2405.113</t>
+          <t>3036097527.9833</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2483.917</t>
+          <t>3028789832.38502</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2498.072</t>
+          <t>3204816808.70155</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2536.244</t>
+          <t>3121818894.97323</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2584.097</t>
+          <t>3193264269.11651</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2651.114</t>
+          <t>3231200343.55448</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2747.62</t>
+          <t>3387551294.97671</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2730.066</t>
+          <t>3167801232.50436</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2610.403</t>
+          <t>3049030804.50615</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>2510.444</t>
+          <t>3018515489.34046</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2443.903</t>
+          <t>2854043535.93157</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2405.928</t>
+          <t>2801152740.35365</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2489.511</t>
+          <t>2776153324.22854</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>1063488230.90022</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>996982615.810266</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>1103003107.61181</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>1129911860.65422</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1232457279.83393</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>1259351363.71908</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>1319401527.87821</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>1388107686.26846</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>1486894693.56668</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1393991378.00972</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1270083920.42409</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>1198891166.15013</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1104695482.03829</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>1004787981.45389</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>945537704.002765</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>5169767.16321785</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4431854.763816</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>3918441.70233614</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>3148520.47856787</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2645901.36715045</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2509032.25912026</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2204697.65453547</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>1816903.57747353</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>1631966.06097545</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1742399.81373109</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1830251.33563411</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1739641.40444603</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1843310.4440662</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>1886065.53839724</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>1915885.26542336</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>15196.3550638555</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>14519.746402162</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>14624.4530036515</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>15740.8772070027</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>18198.5002385541</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>19426.2721027218</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>20686.37464113</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>23518.6248039974</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>26471.077340362</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>23445.5942705464</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>24913.1118875859</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>25646.7876121394</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>23551.8119089058</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>22768.5856934943</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>23155.0163414955</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>24267.752594956</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>23564.3128127579</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>24584.204055909</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>26690.512800098</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>31223.4553673213</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>32655.7273702739</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>35288.1756503391</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>40315.9942082245</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>45876.3891647709</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>39040.8534372518</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>41630.9839515365</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>43768.2423755102</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>40321.9294892239</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>39535.353162466</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>39364.020024182</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>1.27057613788164</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1.37323094954575</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1.18051334887666</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>1.19832810548764</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1.02690352101827</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>1.01392881531493</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.958537219640494</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.909876320277995</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.847891455856336</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.958452572280511</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1.05529962077495</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1.09397155545113</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1.21228658914285</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>1.39446335386965</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>1.63290505440566</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>4297.37964271068</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>4301.58422108436</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>4955.20689103708</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>6159.04417887557</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>7631.69697776228</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>8333.09264368812</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>9321.3323711031</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>11037.5013167068</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>13227.6341513467</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>12595.8632427103</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>12632.6575585243</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>13627.4994010128</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>12594.5153822829</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>13270.2782687269</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>13062.8099043145</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>8.26250375098198</t>
+          <t>853.124733992378</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>8.33742146015543</t>
+          <t>816.710178180487</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>7.84497710826126</t>
+          <t>891.25802583414</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>6.69501075730157</t>
+          <t>887.151676026362</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>6.03039611910988</t>
+          <t>963.873835556199</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>5.94244035252586</t>
+          <t>970.000280150254</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>5.83273391080575</t>
+          <t>998.873129388674</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>5.35551463931815</t>
+          <t>1023.45935328614</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>4.91173222839952</t>
+          <t>1061.55202727724</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>5.26570960989759</t>
+          <t>1001.94883704914</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>5.48696297090356</t>
+          <t>963.922770164458</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>5.33388294586426</t>
+          <t>945.03568140982</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>5.8481042850087</t>
+          <t>881.070881583563</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>5.70102181343767</t>
+          <t>806.423844246209</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>5.73563568952309</t>
+          <t>725.350351347667</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>-128618145.845566</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>-67056430.1211213</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>-65352550.0781563</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>-57450526.883213</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>71309420.0295006</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>149602754.286099</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>231229934.678755</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>326775135.936045</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>369120397.408149</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>344800485.664138</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>358282137.940778</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>330688149.197109</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>338768005.227689</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>282056500.24114</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>246817283.278779</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>-139722620.184845</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>-87946911.9502407</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>-64385924.5683037</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>-6381278.0242247</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>103015580.76668</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>166238805.81436</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>263344844.762032</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>342480852.493224</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>373045589.353309</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>290733969.164445</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>293585325.071503</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>291674129.256136</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>289360774.103395</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>225397549.95688</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>171855711.544532</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>11104474.3392794</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>20890481.8291194</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>-966625.509852627</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>-51069248.8589883</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-31706160.7371797</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-16636051.5282605</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>-32114910.0832777</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>-15705716.5571787</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-3925191.94515995</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>54066516.4996923</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>64696812.869275</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>39014019.9409724</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>49407231.1242936</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>56658950.2842595</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>74961571.7342467</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>1937.08466363972</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>1938.24187166695</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>1943.4000226248</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>1950.25046323922</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>1953.67927110624</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>1953.51151505815</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>1956.33020160649</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>1954.68078360823</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>1961.63292115258</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>1962.26927721235</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>1981.15010397535</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>1978.87783575854</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>1949.18129541159</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>1930.95234273423</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>1909.77860627819</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>1900.69514847139</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>1902.14687268924</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>1906.66348451968</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>1920.67948419275</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>1920.87250020267</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>1923.94157861259</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>1925.54392892608</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>1925.08210126086</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>1931.75230485014</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>1929.26677317738</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>1942.86193786536</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>1940.96424362677</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>1922.82953515665</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>1908.80813782138</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>1889.64738889565</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>7454.06505407591</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>8323.84529712857</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>9378.30535384355</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>12129.7699834328</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>14712.129237295</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>16026.7940222169</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>17961.3757665634</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>21138.1130341771</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>24827.5007767987</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>20005.6397488041</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>20528.3548759714</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>22790.1992543964</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>21186.1671353897</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>22070.913807037</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>23268.5533571211</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>806431923.531734</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>826145445.426997</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>830842324.716918</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>892284481.14951</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>900153430.054341</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>864228102.213935</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>877531536.02096</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>872229070.174027</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>895799761.097334</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>784724103.18791</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>821817402.91933</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>879178823.989772</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>852907682.673801</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>881046899.640059</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>941136941.086145</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>8022.33785310043</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>9099.51105788917</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>11353.492142466</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>14852.7895844677</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>17510.1756775017</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>19092.5979919223</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>21677.0721238431</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>25656.490786923</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>30483.0761756188</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>22416.9174110918</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>21323.2918368754</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>23682.9732557004</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>21574.6859948492</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>22813.0944522302</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>22932.3617206804</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3036.893</t>
+          <t>765612464.079869</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3001.987</t>
+          <t>883265260.916934</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>3056.057</t>
+          <t>1084434176.84738</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>3092.179</t>
+          <t>1249132085.32992</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>3137.303</t>
+          <t>1357579230.26298</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>3149.281</t>
+          <t>1400404421.73386</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>3240.171</t>
+          <t>1535200623.16696</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>3310.082</t>
+          <t>1640904718.24241</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>3438.268</t>
+          <t>1751817037.81783</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>3410.056</t>
+          <t>1364262084.57944</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>3294.414</t>
+          <t>1248847898.47549</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>3167.11</t>
+          <t>1283118476.05445</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>3022.4</t>
+          <t>1223895188.26276</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>2923.053</t>
+          <t>1224993920.67035</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2966.935</t>
+          <t>1160192841.29982</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2414.731</t>
+          <t>-568.272799024517</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2366.07</t>
+          <t>-775.665760760598</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2405.113</t>
+          <t>-1975.18678862241</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2483.917</t>
+          <t>-2723.01960103483</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2498.072</t>
+          <t>-2798.04644020663</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2536.244</t>
+          <t>-3065.80396970543</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2584.097</t>
+          <t>-3715.69635727967</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2651.114</t>
+          <t>-4518.37775274596</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2747.62</t>
+          <t>-5655.57539882013</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2730.066</t>
+          <t>-2411.27766228772</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2610.403</t>
+          <t>-794.936960904028</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>2510.444</t>
+          <t>-892.774001304011</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2443.903</t>
+          <t>-388.518859459501</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>2405.928</t>
+          <t>-742.180645193217</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2489.511</t>
+          <t>336.191636440768</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2986.708</t>
+          <t>40819459.4518647</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2927.801</t>
+          <t>-57119815.4899367</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>3036.426</t>
+          <t>-253591852.130462</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>3028.853</t>
+          <t>-356847604.180409</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>3204.879</t>
+          <t>-457425800.20864</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>3121.824</t>
+          <t>-536176319.519923</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>3193.371</t>
+          <t>-657669087.146003</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>3231.585</t>
+          <t>-768675648.068382</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>3387.849</t>
+          <t>-856017276.720499</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>3168.019</t>
+          <t>-579537981.391528</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>3049.486</t>
+          <t>-427030495.556163</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>3019.204</t>
+          <t>-403939652.06468</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2854.184</t>
+          <t>-370987505.58896</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>2801.254</t>
+          <t>-343947021.030287</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2776.058</t>
+          <t>-219055900.213674</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>8847.92482570321</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>9208.13332802637</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>10428.6242276699</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>13279.9045178944</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>16700.0836586941</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>17829.839281176</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>19442.4926539623</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>22580.9737842677</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>26706.4042391082</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>24103.1664725168</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>22322.2894162977</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>23221.9878162258</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>20768.4318814021</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>20934.0222451293</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>20515.3573591194</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1870.236</t>
+          <t>-0.00329451693364894</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1803.921</t>
+          <t>0.0120204382522571</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1806.089</t>
+          <t>0.00874218599123273</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1786.246</t>
+          <t>0.0120457932793649</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1867.918</t>
+          <t>0.0162604928085887</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1857.111</t>
+          <t>0.0183439621715205</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1871.932</t>
+          <t>0.021303344806549</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>1884.944</t>
+          <t>0.0225350984370707</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>1954.647</t>
+          <t>0.0215897595010146</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1902.391</t>
+          <t>0.0114413552462448</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1824.623</t>
+          <t>0.0164942731023428</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1768.753</t>
+          <t>0.0186745591235532</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1667.031</t>
+          <t>0.0155103182865531</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>1613.196</t>
+          <t>0.0175524085987038</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>1633.011</t>
+          <t>0.0212817041853491</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>11053.0420753764</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>11170.9246754236</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>13222.969897812</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>17055.7280606209</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>20099.0058384702</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>21770.3847498731</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>23824.2163175168</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>28528.2800988921</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>33710.4164008488</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>31156.3227547357</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>28959.0378783993</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>29897.7428783456</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>27043.1761608207</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>27375.2798803056</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>27133.60860391</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1063.52</t>
+          <t>14058.2773338164</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>997.039</t>
+          <t>14227.5935239663</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1103.116</t>
+          <t>16837.9436053174</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1129.992</t>
+          <t>21722.6100515903</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1232.457</t>
+          <t>25598.350673904</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1259.359</t>
+          <t>27722.0047107369</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>1319.459</t>
+          <t>30330.7892984034</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>1388.279</t>
+          <t>36306.3519428676</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>1486.963</t>
+          <t>42887.1134134228</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>1394.057</t>
+          <t>39528.1836597952</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1270.214</t>
+          <t>35505.8379457055</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1199.064</t>
+          <t>36441.0535508881</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1104.751</t>
+          <t>32770.4694782475</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>1004.792</t>
+          <t>32562.3595582048</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>945.485</t>
+          <t>31714.0152300433</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>127.05</t>
+          <t>67128.8973838885</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>137.31</t>
+          <t>68348.7251160496</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>118.03</t>
+          <t>77624.0784561411</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>119.82</t>
+          <t>98466.1562108934</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>102.69</t>
+          <t>119748.231412554</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>101.39</t>
+          <t>129901.630369209</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>95.85</t>
+          <t>143914.59109527</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>90.96</t>
+          <t>171975.873266776</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>84.78</t>
+          <t>200442.140863078</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>95.84</t>
+          <t>188542.672866955</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>105.51</t>
+          <t>174065.868749431</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>109.37</t>
+          <t>181737.676074269</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>121.22</t>
+          <t>162149.66181013</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>139.45</t>
+          <t>162405.748038515</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>163.31</t>
+          <t>158969.7574768</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>21229.742838981</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>4.432</t>
+          <t>21007.2715173725</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>3.919</t>
+          <t>22000.3339861121</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>3.149</t>
+          <t>23280.475246785</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2.646</t>
+          <t>23433.9451083522</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2.509</t>
+          <t>24125.4542300619</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2.205</t>
+          <t>24752.266969072</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>1.817</t>
+          <t>25945.3535809917</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.632</t>
+          <t>26614.6608425461</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.743</t>
+          <t>25443.5333014708</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>23591.9546290086</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>23247.1951371186</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1.843</t>
+          <t>22604.4129087252</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>1.886</t>
+          <t>21877.0072135027</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>1.916</t>
+          <t>21481.8922695116</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>16941.8953023991</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>16623.7383861454</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>17610.7335393892</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>18378.4773554916</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>18511.9454223155</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>18961.53244261</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>19460.537877538</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>20507.9131040109</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>20992.9220926295</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>20050.4162058117</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>19241.7969635339</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>19046.3054961218</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>18747.345764815</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>18444.8126801896</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>18440.7530522589</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>4076.22235354227</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>5123.16585096234</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>5633.81102229871</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>7345.14714160564</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>9578.86223348733</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>10716.0032371997</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>12387.1945278991</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>14912.9945495748</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>17555.131766449</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>14753.0469420576</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>15503.747535474</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>17021.3703778389</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>15109.508247015</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>16120.8903170771</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>16445.9572573525</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2414731000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2366070000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2405113000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2483917000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2498072000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2536244000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>2584097000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>2651114000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>2747620000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>2730066000</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>2610403000</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>2510444000</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>2443903000</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>2405928000</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2489511000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>3036892694.32461</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>3001987215.94689</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>3056057432.89268</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>3092178728.78127</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>3137303428.40601</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>3149280730.61517</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>3240170535.52178</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>3310082419.01299</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>3438267974.83361</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>3410056192.26195</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>3294413844.9414</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>3167110175.61067</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>3022399604.83598</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>2923053341.85277</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2966935365.30506</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>1870236338.19224</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1803920705.62594</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1806089207.18025</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>1786245517.06687</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>1867918165.0958</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>1857110779.42097</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>1871931880.34484</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>1884943929.55098</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>1954646692.04246</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1902391364.12336</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1824622873.9101</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>1768753357.6259</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1667030754.46954</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>1613196319.4364</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>1633010946.27834</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>1597780</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1578210</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>1602830</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>1609940</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>1633270</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>1636890</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>1682730</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>1719450</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>1779870</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1767540</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>1695650</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>1631720</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1571850</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>1531350</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>1570100</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>1246580</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1220730</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>1237580</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>1273640</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>1278650</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>1298300</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>1320890</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>1356290</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>1400680</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1391280</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>1317620</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>1268620</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1253810</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>1245980</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>1303560</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>3036892694.32461</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3001987215.94689</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>3056057432.89268</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>3092178728.78127</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>3137303428.40601</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>3149280730.61517</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>3240170535.52178</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>3310082419.01299</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>3438267974.83361</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>3410056192.26195</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>3294413844.9414</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>3167110175.61067</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>3022399604.83598</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>2923053341.85277</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2966935365.30506</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2414731000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2366070000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2405113000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2483917000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2498072000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2536244000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>2584097000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>2651114000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>2747620000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>2730066000</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>2610403000</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>2510444000</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>2443903000</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>2405928000</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2489511000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>37083.09416</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>39465.1509445828</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>45977.3466223032</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>60003.324960004</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>72910.0751952982</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>80749.9531516706</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>90930.500567504</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>109151.911487152</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>127195.753066674</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>109795.537316528</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>101456.362365074</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>108097.178513553</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>97843.0746179348</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>98723.9680275546</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>97418.5872655664</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>18134.51656</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>19350.7809845828</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>22471.7163823032</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>29067.719840004</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>35177.2394252981</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>38437.9877416706</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>42717.971767504</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>51219.3689371525</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>60442.3184266741</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>54281.241996528</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>51009.6328350742</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>53462.4313135533</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>47879.9006979348</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>48683.2849875546</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>48159.9882282878</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>97169.92400277</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>95964.6251035126</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>99789.258571368</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>102141.951619121</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>105536.738975571</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>107891.313005937</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>113496.561002833</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>114656.405770721</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>120349.69887856</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>120164.755944749</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>115660.083153095</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>114086.067572887</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>110110.943252265</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>107062.555855051</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>105620.478895896</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD16</t>
